--- a/Code and data/Initial data/Non sector data/FINANCE-GFCF.xlsx
+++ b/Code and data/Initial data/Non sector data/FINANCE-GFCF.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N233"/>
+  <dimension ref="A1:N238"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>NL32</t>
+          <t>NL31</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="M187">
-        <v>3038.99</v>
+        <v>1324.13</v>
       </c>
     </row>
     <row r="188">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>NL34</t>
+          <t>NL32</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="M188">
-        <v>770.8200000000001</v>
+        <v>3038.99</v>
       </c>
     </row>
     <row r="189">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>NL41</t>
+          <t>NL33</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -8507,7 +8507,7 @@
         </is>
       </c>
       <c r="M189">
-        <v>4237.8</v>
+        <v>3532.92</v>
       </c>
     </row>
     <row r="190">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>NL42</t>
+          <t>NL34</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -8550,18 +8550,18 @@
         </is>
       </c>
       <c r="M190">
-        <v>1559.58</v>
+        <v>770.8200000000001</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>PL21</t>
+          <t>NL41</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -8593,18 +8593,18 @@
         </is>
       </c>
       <c r="M191">
-        <v>1652.14</v>
+        <v>4237.8</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>PL22</t>
+          <t>NL42</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -8636,7 +8636,7 @@
         </is>
       </c>
       <c r="M192">
-        <v>4197.27</v>
+        <v>1559.58</v>
       </c>
     </row>
     <row r="193">
@@ -8647,7 +8647,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>PL41</t>
+          <t>PL21</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="M193">
-        <v>2853.37</v>
+        <v>1652.14</v>
       </c>
     </row>
     <row r="194">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>PL42</t>
+          <t>PL22</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -8722,7 +8722,7 @@
         </is>
       </c>
       <c r="M194">
-        <v>756.27</v>
+        <v>4197.27</v>
       </c>
     </row>
     <row r="195">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>PL43</t>
+          <t>PL41</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="M195">
-        <v>759.36</v>
+        <v>2853.37</v>
       </c>
     </row>
     <row r="196">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>PL51</t>
+          <t>PL42</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="M196">
-        <v>2337.3</v>
+        <v>756.27</v>
       </c>
     </row>
     <row r="197">
@@ -8819,7 +8819,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>PL52</t>
+          <t>PL43</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="M197">
-        <v>1188.24</v>
+        <v>759.36</v>
       </c>
     </row>
     <row r="198">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>PL61</t>
+          <t>PL51</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="M198">
-        <v>1236.46</v>
+        <v>2337.3</v>
       </c>
     </row>
     <row r="199">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>PL62</t>
+          <t>PL52</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -8937,7 +8937,7 @@
         </is>
       </c>
       <c r="M199">
-        <v>683.84</v>
+        <v>1188.24</v>
       </c>
     </row>
     <row r="200">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>PL63</t>
+          <t>PL61</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -8980,7 +8980,7 @@
         </is>
       </c>
       <c r="M200">
-        <v>1560.33</v>
+        <v>1236.46</v>
       </c>
     </row>
     <row r="201">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>PL71</t>
+          <t>PL62</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="M201">
-        <v>1531.26</v>
+        <v>683.84</v>
       </c>
     </row>
     <row r="202">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>PL72</t>
+          <t>PL63</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -9066,7 +9066,7 @@
         </is>
       </c>
       <c r="M202">
-        <v>629.9</v>
+        <v>1560.33</v>
       </c>
     </row>
     <row r="203">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>PL81</t>
+          <t>PL71</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M203">
-        <v>819.9</v>
+        <v>1531.26</v>
       </c>
     </row>
     <row r="204">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>PL82</t>
+          <t>PL72</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="M204">
-        <v>1209.38</v>
+        <v>629.9</v>
       </c>
     </row>
     <row r="205">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>PL84</t>
+          <t>PL81</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -9195,7 +9195,7 @@
         </is>
       </c>
       <c r="M205">
-        <v>446.06</v>
+        <v>819.9</v>
       </c>
     </row>
     <row r="206">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>PL91</t>
+          <t>PL82</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -9238,7 +9238,7 @@
         </is>
       </c>
       <c r="M206">
-        <v>1738.66</v>
+        <v>1209.38</v>
       </c>
     </row>
     <row r="207">
@@ -9249,7 +9249,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>PL92</t>
+          <t>PL84</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -9281,18 +9281,18 @@
         </is>
       </c>
       <c r="M207">
-        <v>3241.08</v>
+        <v>446.06</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>PT11</t>
+          <t>PL91</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -9324,18 +9324,18 @@
         </is>
       </c>
       <c r="M208">
-        <v>3831.03</v>
+        <v>1738.66</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>PT15</t>
+          <t>PL92</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="M209">
-        <v>52.11</v>
+        <v>3241.08</v>
       </c>
     </row>
     <row r="210">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>PT20</t>
+          <t>PT11</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="M210">
-        <v>72.44</v>
+        <v>3831.03</v>
       </c>
     </row>
     <row r="211">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>PT30</t>
+          <t>PT15</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -9453,18 +9453,18 @@
         </is>
       </c>
       <c r="M211">
-        <v>38</v>
+        <v>52.11</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>RO11</t>
+          <t>PT16</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -9496,18 +9496,18 @@
         </is>
       </c>
       <c r="M212">
-        <v>1026.26</v>
+        <v>2985.2</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>RO12</t>
+          <t>PT17</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -9539,18 +9539,18 @@
         </is>
       </c>
       <c r="M213">
-        <v>1159.46</v>
+        <v>1738.62</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>RO21</t>
+          <t>PT18</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -9582,18 +9582,18 @@
         </is>
       </c>
       <c r="M214">
-        <v>619.9299999999999</v>
+        <v>913.21</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>RO22</t>
+          <t>PT20</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -9625,18 +9625,18 @@
         </is>
       </c>
       <c r="M215">
-        <v>568.8200000000001</v>
+        <v>72.44</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>RO31</t>
+          <t>PT30</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -9668,7 +9668,7 @@
         </is>
       </c>
       <c r="M216">
-        <v>1627.95</v>
+        <v>38</v>
       </c>
     </row>
     <row r="217">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>RO32</t>
+          <t>RO11</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -9711,7 +9711,7 @@
         </is>
       </c>
       <c r="M217">
-        <v>1151.54</v>
+        <v>1026.26</v>
       </c>
     </row>
     <row r="218">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>RO41</t>
+          <t>RO12</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -9754,7 +9754,7 @@
         </is>
       </c>
       <c r="M218">
-        <v>531.12</v>
+        <v>1159.46</v>
       </c>
     </row>
     <row r="219">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>RO42</t>
+          <t>RO21</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -9797,18 +9797,18 @@
         </is>
       </c>
       <c r="M219">
-        <v>880.1</v>
+        <v>619.9299999999999</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>SE11</t>
+          <t>RO22</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -9840,18 +9840,18 @@
         </is>
       </c>
       <c r="M220">
-        <v>3118.18</v>
+        <v>568.8200000000001</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>SE12</t>
+          <t>RO31</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -9883,18 +9883,18 @@
         </is>
       </c>
       <c r="M221">
-        <v>3613.71</v>
+        <v>1627.95</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>SE21</t>
+          <t>RO32</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -9926,18 +9926,18 @@
         </is>
       </c>
       <c r="M222">
-        <v>1769.35</v>
+        <v>1151.54</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>SE22</t>
+          <t>RO41</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -9969,18 +9969,18 @@
         </is>
       </c>
       <c r="M223">
-        <v>1969.2</v>
+        <v>531.12</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>SE23</t>
+          <t>RO42</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -10012,7 +10012,7 @@
         </is>
       </c>
       <c r="M224">
-        <v>7348.07</v>
+        <v>880.1</v>
       </c>
     </row>
     <row r="225">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>SE31</t>
+          <t>SE11</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -10055,7 +10055,7 @@
         </is>
       </c>
       <c r="M225">
-        <v>1288.55</v>
+        <v>3118.18</v>
       </c>
     </row>
     <row r="226">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>SE32</t>
+          <t>SE12</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -10098,7 +10098,7 @@
         </is>
       </c>
       <c r="M226">
-        <v>685.96</v>
+        <v>3613.71</v>
       </c>
     </row>
     <row r="227">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>SE33</t>
+          <t>SE21</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -10141,18 +10141,18 @@
         </is>
       </c>
       <c r="M227">
-        <v>2262.08</v>
+        <v>1769.35</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>SI03</t>
+          <t>SE22</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -10184,18 +10184,18 @@
         </is>
       </c>
       <c r="M228">
-        <v>1605.25</v>
+        <v>1969.2</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>SI04</t>
+          <t>SE23</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -10227,18 +10227,18 @@
         </is>
       </c>
       <c r="M229">
-        <v>1358.35</v>
+        <v>7348.07</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>SK01</t>
+          <t>SE31</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -10270,18 +10270,18 @@
         </is>
       </c>
       <c r="M230">
-        <v>1171.62</v>
+        <v>1288.55</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>SK02</t>
+          <t>SE32</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -10313,18 +10313,18 @@
         </is>
       </c>
       <c r="M231">
-        <v>2136.43</v>
+        <v>685.96</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>SK03</t>
+          <t>SE33</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -10356,49 +10356,264 @@
         </is>
       </c>
       <c r="M232">
-        <v>994.6799999999999</v>
+        <v>2262.08</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>SI03</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>GFCF</t>
+        </is>
+      </c>
+      <c r="J233">
+        <v>2023</v>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Eurostat nama_10r_2gfcf</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>Million euro</t>
+        </is>
+      </c>
+      <c r="M233">
+        <v>1605.25</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>SI04</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>GFCF</t>
+        </is>
+      </c>
+      <c r="J234">
+        <v>2023</v>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Eurostat nama_10r_2gfcf</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>Million euro</t>
+        </is>
+      </c>
+      <c r="M234">
+        <v>1358.35</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr">
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>SK01</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>GFCF</t>
+        </is>
+      </c>
+      <c r="J235">
+        <v>2023</v>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Eurostat nama_10r_2gfcf</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>Million euro</t>
+        </is>
+      </c>
+      <c r="M235">
+        <v>1171.62</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>SK02</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>GFCF</t>
+        </is>
+      </c>
+      <c r="J236">
+        <v>2023</v>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Eurostat nama_10r_2gfcf</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>Million euro</t>
+        </is>
+      </c>
+      <c r="M236">
+        <v>2136.43</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>SK03</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>GFCF</t>
+        </is>
+      </c>
+      <c r="J237">
+        <v>2023</v>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Eurostat nama_10r_2gfcf</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>Million euro</t>
+        </is>
+      </c>
+      <c r="M237">
+        <v>994.6799999999999</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
         <is>
           <t>SK04</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>Vulnerability</t>
-        </is>
-      </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>GFCF</t>
-        </is>
-      </c>
-      <c r="J233">
-        <v>2023</v>
-      </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>Eurostat nama_10r_2gfcf</t>
-        </is>
-      </c>
-      <c r="L233" t="inlineStr">
-        <is>
-          <t>Million euro</t>
-        </is>
-      </c>
-      <c r="M233">
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>GFCF</t>
+        </is>
+      </c>
+      <c r="J238">
+        <v>2023</v>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Eurostat nama_10r_2gfcf</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>Million euro</t>
+        </is>
+      </c>
+      <c r="M238">
         <v>918.33</v>
       </c>
     </row>
